--- a/outputs/daily/hr_rankings_2026-08-16.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-16.xlsx
@@ -4096,7 +4096,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>78</v>
       </c>
       <c r="U14" t="n">
-        <v>50.3</v>
+        <v>48.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Contact streak: 9/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -10477,7 +10477,7 @@
         <v>78</v>
       </c>
       <c r="U37" t="n">
-        <v>51.3</v>
+        <v>49.9</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -15721,7 +15721,7 @@
         <v>78</v>
       </c>
       <c r="U56" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 4/27, 0 HR</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
@@ -16743,27 +16743,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>608369</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Corey Seager</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-16T20:05:00Z</t>
+          <t>2026-08-16T20:10:00Z</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -16773,17 +16773,17 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Tarik Skubal</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>669373</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -16806,26 +16806,26 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>61.8</v>
+        <v>51.8</v>
       </c>
       <c r="Q60" t="n">
-        <v>20.8</v>
+        <v>28.8</v>
       </c>
       <c r="R60" t="n">
-        <v>30.9</v>
+        <v>27.6</v>
       </c>
       <c r="S60" t="n">
-        <v>92.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T60" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U60" t="n">
-        <v>37.8</v>
+        <v>34.9</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -16886,7 +16886,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -16896,119 +16896,119 @@
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.3% barrel, 14.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>15.51</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>48.35</t>
+          <t>46.01</t>
         </is>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>91.85</t>
+          <t>91.12</t>
         </is>
       </c>
       <c r="AQ60" t="inlineStr">
         <is>
-          <t>102.4607</t>
+          <t>102.0793</t>
         </is>
       </c>
       <c r="AR60" t="inlineStr">
         <is>
-          <t>0.4913</t>
+          <t>0.4596</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>0.2441</t>
+          <t>0.2056</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>0.3294</t>
         </is>
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>71.94</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>15.86</t>
+          <t>44.17</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>31.43</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>27.59</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>0.1978</t>
+          <t>0.1937</t>
         </is>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
         <is>
-          <t>85.57</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD60" t="inlineStr">
         <is>
-          <t>0.3375</t>
+          <t>0.3447</t>
         </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
-          <t>0.1282</t>
+          <t>0.1254</t>
         </is>
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>26.18</t>
         </is>
       </c>
       <c r="BG60" t="inlineStr"/>
       <c r="BH60" t="inlineStr"/>
       <c r="BI60" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ60" t="inlineStr"/>
@@ -17019,27 +17019,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>683357</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Owen Caissie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-16T20:10:00Z</t>
+          <t>2026-08-16T17:40:00Z</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -17049,17 +17049,17 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Tarik Skubal</t>
+          <t>Nick Lodolo</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>669373</t>
+          <t>666157</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -17068,7 +17068,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -17082,26 +17082,26 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>51.8</v>
+        <v>46.8</v>
       </c>
       <c r="Q61" t="n">
-        <v>28.8</v>
+        <v>47.6</v>
       </c>
       <c r="R61" t="n">
-        <v>27.6</v>
+        <v>39.3</v>
       </c>
       <c r="S61" t="n">
-        <v>88.7</v>
+        <v>71.7</v>
       </c>
       <c r="T61" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U61" t="n">
-        <v>34.9</v>
+        <v>37.8</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -17115,7 +17115,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -17157,12 +17157,12 @@
       </c>
       <c r="AH61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -17172,12 +17172,12 @@
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 5/20, 1 HR</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 13.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
@@ -17187,104 +17187,104 @@
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>46.01</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>91.12</t>
+          <t>89.96</t>
         </is>
       </c>
       <c r="AQ61" t="inlineStr">
         <is>
-          <t>102.0793</t>
+          <t>100.2726</t>
         </is>
       </c>
       <c r="AR61" t="inlineStr">
         <is>
-          <t>0.4596</t>
+          <t>0.3817</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>0.2056</t>
+          <t>0.1783</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr">
         <is>
-          <t>0.3294</t>
+          <t>0.2803</t>
         </is>
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>74.81</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>44.17</t>
+          <t>54.09</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>27.59</t>
+          <t>31.32</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>9.4</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>0.1937</t>
+          <t>0.1904</t>
         </is>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="BD61" t="inlineStr">
         <is>
-          <t>0.3447</t>
+          <t>0.4489</t>
         </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
-          <t>0.1254</t>
+          <t>0.1778</t>
         </is>
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>26.18</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="BG61" t="inlineStr"/>
       <c r="BH61" t="inlineStr"/>
       <c r="BI61" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ61" t="inlineStr"/>
@@ -17295,27 +17295,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>683357</t>
+          <t>608369</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Owen Caissie</t>
+          <t>Corey Seager</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-16T17:40:00Z</t>
+          <t>2026-08-16T20:05:00Z</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -17325,17 +17325,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Nick Lodolo</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>666157</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -17358,26 +17358,26 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>46.8</v>
+        <v>61.8</v>
       </c>
       <c r="Q62" t="n">
-        <v>47.6</v>
+        <v>20.8</v>
       </c>
       <c r="R62" t="n">
-        <v>39.3</v>
+        <v>30.9</v>
       </c>
       <c r="S62" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T62" t="n">
         <v>50</v>
       </c>
       <c r="U62" t="n">
-        <v>37.8</v>
+        <v>36.3</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -17433,12 +17433,12 @@
       </c>
       <c r="AH62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -17448,119 +17448,119 @@
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 15.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>15.51</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>48.35</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>89.96</t>
+          <t>91.85</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
         <is>
-          <t>100.2726</t>
+          <t>102.4607</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.4913</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>0.1783</t>
+          <t>0.2441</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr">
         <is>
-          <t>0.2803</t>
+          <t>0.358</t>
         </is>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>74.81</t>
+          <t>71.94</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>54.09</t>
+          <t>15.86</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>41.69</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.1904</t>
+          <t>0.1978</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>85.57</t>
         </is>
       </c>
       <c r="BD62" t="inlineStr">
         <is>
-          <t>0.4489</t>
+          <t>0.3375</t>
         </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
-          <t>0.1778</t>
+          <t>0.1282</t>
         </is>
       </c>
       <c r="BF62" t="inlineStr">
         <is>
-          <t>25.56</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="BG62" t="inlineStr"/>
       <c r="BH62" t="inlineStr"/>
       <c r="BI62" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ62" t="inlineStr"/>
@@ -23919,27 +23919,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>661531</t>
+          <t>671277</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brian Serven</t>
+          <t>Luis Garcia</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-16T20:05:00Z</t>
+          <t>2026-08-16T17:37:00Z</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -23949,26 +23949,26 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Cody Bradford</t>
+          <t>Dylan Cease</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>674003</t>
+          <t>656302</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -23982,26 +23982,26 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>44.3</v>
+        <v>49.9</v>
       </c>
       <c r="Q86" t="n">
-        <v>50.8</v>
+        <v>20.4</v>
       </c>
       <c r="R86" t="n">
-        <v>30.9</v>
+        <v>30.4</v>
       </c>
       <c r="S86" t="n">
-        <v>47.9</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T86" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U86" t="n">
-        <v>27.6</v>
+        <v>14.1</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -24040,7 +24040,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD86" t="inlineStr"/>
@@ -24057,134 +24057,134 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>11.31</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>99.6869</t>
+          <t>101.8155</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>0.4903</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>0.2065</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>41.08</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>0.2356</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>86.87</t>
         </is>
       </c>
       <c r="BD86" t="inlineStr">
         <is>
-          <t>0.453</t>
+          <t>0.3051</t>
         </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>0.1093</t>
         </is>
       </c>
       <c r="BF86" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>24.63</t>
         </is>
       </c>
       <c r="BG86" t="inlineStr"/>
       <c r="BH86" t="inlineStr"/>
       <c r="BI86" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ86" t="inlineStr"/>
@@ -24195,27 +24195,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>671277</t>
+          <t>661531</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Luis Garcia</t>
+          <t>Brian Serven</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-16T17:37:00Z</t>
+          <t>2026-08-16T20:05:00Z</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -24225,22 +24225,22 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Dylan Cease</t>
+          <t>Cody Bradford</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>656302</t>
+          <t>674003</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L87" t="n">
@@ -24258,26 +24258,26 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>49.9</v>
+        <v>44.3</v>
       </c>
       <c r="Q87" t="n">
-        <v>20.4</v>
+        <v>50.8</v>
       </c>
       <c r="R87" t="n">
-        <v>30.4</v>
+        <v>30.9</v>
       </c>
       <c r="S87" t="n">
-        <v>90.40000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T87" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U87" t="n">
-        <v>14.1</v>
+        <v>26.4</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -24316,7 +24316,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr"/>
@@ -24333,134 +24333,134 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/28, 0 HR</t>
+          <t>Last 7 games: 4/23, 1 HR</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.9% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>101.8155</t>
+          <t>99.6869</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>0.4903</t>
+          <t>0.443</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>0.2065</t>
+          <t>0.192</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.309</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>0.2356</t>
+          <t>0.222</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>86.87</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="BD87" t="inlineStr">
         <is>
-          <t>0.3051</t>
+          <t>0.453</t>
         </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
-          <t>0.1093</t>
+          <t>0.185</t>
         </is>
       </c>
       <c r="BF87" t="inlineStr">
         <is>
-          <t>24.63</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="BG87" t="inlineStr"/>
       <c r="BH87" t="inlineStr"/>
       <c r="BI87" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ87" t="inlineStr"/>
@@ -24471,27 +24471,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>671732</t>
+          <t>691723</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Coby Mayo</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-16T20:05:00Z</t>
+          <t>2026-08-16T16:15:00Z</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -24501,26 +24501,26 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Cody Bradford</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>674003</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
@@ -24534,26 +24534,26 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>35.5</v>
+        <v>47.3</v>
       </c>
       <c r="Q88" t="n">
-        <v>50.8</v>
+        <v>35</v>
       </c>
       <c r="R88" t="n">
-        <v>30.9</v>
+        <v>27.6</v>
       </c>
       <c r="S88" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T88" t="n">
         <v>50</v>
       </c>
       <c r="U88" t="n">
-        <v>65.8</v>
+        <v>19.5</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -24592,7 +24592,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr"/>
@@ -24614,129 +24614,129 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 20.3 HR allowed</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>11.01</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>44.68</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>89.73</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>101.7826</t>
+          <t>102.6095</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>0.3973</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.1465</t>
+          <t>0.1845</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.3075</t>
+          <t>0.2974</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>75.33</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>38.51</t>
+          <t>54.04</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>50.04</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>23.12</t>
+          <t>33.9</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>0.1483</t>
+          <t>0.2032</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>87.93</t>
         </is>
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>0.453</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>0.1438</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="BG88" t="inlineStr"/>
       <c r="BH88" t="inlineStr"/>
       <c r="BI88" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ88" t="inlineStr"/>
@@ -24747,27 +24747,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>691723</t>
+          <t>672640</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Coby Mayo</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-16T16:15:00Z</t>
+          <t>2026-08-16T17:40:00Z</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -24777,22 +24777,22 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Nick Lodolo</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>666157</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -24810,26 +24810,26 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>47.3</v>
+        <v>29.7</v>
       </c>
       <c r="Q89" t="n">
-        <v>35</v>
+        <v>47.6</v>
       </c>
       <c r="R89" t="n">
-        <v>27.6</v>
+        <v>39.3</v>
       </c>
       <c r="S89" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T89" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U89" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -24885,12 +24885,12 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -24900,12 +24900,12 @@
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 20.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
@@ -24915,104 +24915,104 @@
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>11.01</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>40.33</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>102.6095</t>
+          <t>100.2216</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>0.3973</t>
+          <t>0.4221</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>0.1845</t>
+          <t>0.1454</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>0.2974</t>
+          <t>0.323</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>75.33</t>
+          <t>71.77</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>54.04</t>
+          <t>23.37</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>50.04</t>
+          <t>32.65</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>33.9</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>0.2032</t>
+          <t>0.1388</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>39.45</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>87.93</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="BD89" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.4489</t>
         </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
-          <t>0.1438</t>
+          <t>0.1778</t>
         </is>
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>25.56</t>
         </is>
       </c>
       <c r="BG89" t="inlineStr"/>
       <c r="BH89" t="inlineStr"/>
       <c r="BI89" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ89" t="inlineStr"/>
@@ -25023,27 +25023,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>672640</t>
+          <t>671732</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-16T17:40:00Z</t>
+          <t>2026-08-16T20:05:00Z</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -25053,17 +25053,17 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Nick Lodolo</t>
+          <t>Cody Bradford</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>666157</t>
+          <t>674003</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -25086,26 +25086,26 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>29.7</v>
+        <v>35.5</v>
       </c>
       <c r="Q90" t="n">
-        <v>47.6</v>
+        <v>50.8</v>
       </c>
       <c r="R90" t="n">
-        <v>39.3</v>
+        <v>30.9</v>
       </c>
       <c r="S90" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T90" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U90" t="n">
-        <v>13</v>
+        <v>64.8</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr"/>
@@ -25161,134 +25161,134 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 15.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>40.33</t>
+          <t>44.82</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>89.73</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>100.2216</t>
+          <t>101.7826</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>0.4221</t>
+          <t>0.379</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>0.1454</t>
+          <t>0.1465</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>0.3075</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>71.77</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>38.51</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>0.1388</t>
+          <t>0.1483</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>39.45</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="BD90" t="inlineStr">
         <is>
-          <t>0.4489</t>
+          <t>0.453</t>
         </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
-          <t>0.1778</t>
+          <t>0.185</t>
         </is>
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>25.56</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="BG90" t="inlineStr"/>
       <c r="BH90" t="inlineStr"/>
       <c r="BI90" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ90" t="inlineStr"/>
@@ -25851,27 +25851,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>607043</t>
+          <t>680777</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-16T20:05:00Z</t>
+          <t>2026-08-16T18:10:00Z</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -25881,26 +25881,26 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Andrew Painter</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>691725</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>45.7</v>
+        <v>45.6</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -25914,26 +25914,26 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>49.8</v>
+        <v>38.8</v>
       </c>
       <c r="Q93" t="n">
-        <v>20.8</v>
+        <v>40.9</v>
       </c>
       <c r="R93" t="n">
-        <v>30.9</v>
+        <v>27.1</v>
       </c>
       <c r="S93" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T93" t="n">
         <v>50</v>
       </c>
       <c r="U93" t="n">
-        <v>34.9</v>
+        <v>30</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr">
@@ -25972,7 +25972,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr"/>
@@ -25989,134 +25989,134 @@
       </c>
       <c r="AH93" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL93" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.3% barrel, 14.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AQ93" t="inlineStr">
         <is>
-          <t>102.1553</t>
+          <t>100.8636</t>
         </is>
       </c>
       <c r="AR93" t="inlineStr">
         <is>
-          <t>0.4722</t>
+          <t>0.4301</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>0.1936</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr">
         <is>
-          <t>0.3539</t>
+          <t>0.3502</t>
         </is>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.93</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>27.25</t>
+          <t>35.35</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>32.89</t>
+          <t>37.11</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>25.7</t>
+          <t>27.19</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>0.1684</t>
+          <t>0.1856</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>85.57</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="BD93" t="inlineStr">
         <is>
-          <t>0.3375</t>
+          <t>0.442</t>
         </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
-          <t>0.1282</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF93" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="BG93" t="inlineStr"/>
       <c r="BH93" t="inlineStr"/>
       <c r="BI93" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ93" t="inlineStr"/>
@@ -26127,27 +26127,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>680777</t>
+          <t>607043</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-16T18:10:00Z</t>
+          <t>2026-08-16T20:05:00Z</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -26157,22 +26157,22 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Andrew Painter</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>691725</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -26190,26 +26190,26 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>38.8</v>
+        <v>49.8</v>
       </c>
       <c r="Q94" t="n">
-        <v>40.9</v>
+        <v>20.8</v>
       </c>
       <c r="R94" t="n">
-        <v>27.1</v>
+        <v>30.9</v>
       </c>
       <c r="S94" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T94" t="n">
         <v>50</v>
       </c>
       <c r="U94" t="n">
-        <v>30</v>
+        <v>33.7</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
@@ -26248,7 +26248,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD94" t="inlineStr"/>
@@ -26265,134 +26265,134 @@
       </c>
       <c r="AH94" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 15.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AQ94" t="inlineStr">
         <is>
-          <t>100.8636</t>
+          <t>102.1553</t>
         </is>
       </c>
       <c r="AR94" t="inlineStr">
         <is>
-          <t>0.4301</t>
+          <t>0.4722</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1936</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr">
         <is>
-          <t>0.3502</t>
+          <t>0.3539</t>
         </is>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>72.93</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>27.25</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>32.89</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>27.19</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>0.1856</t>
+          <t>0.1684</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>85.57</t>
         </is>
       </c>
       <c r="BD94" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>0.3375</t>
         </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1282</t>
         </is>
       </c>
       <c r="BF94" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="BG94" t="inlineStr"/>
       <c r="BH94" t="inlineStr"/>
       <c r="BI94" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ94" t="inlineStr"/>
@@ -28754,7 +28754,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -28764,7 +28764,7 @@
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 3/26, 0 HR</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
@@ -30040,7 +30040,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>50</v>
       </c>
       <c r="U108" t="n">
-        <v>21.8</v>
+        <v>19.1</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
@@ -30144,7 +30144,7 @@
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/14, 1 HR</t>
+          <t>Last 7 games: 2/16, 1 HR</t>
         </is>
       </c>
       <c r="AL108" t="inlineStr">
@@ -30267,27 +30267,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>694671</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-16T20:10:00Z</t>
+          <t>2026-08-16T20:05:00Z</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -30297,22 +30297,22 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Logan Henderson</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>701656</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L109" t="n">
@@ -30330,26 +30330,26 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>36.4</v>
+        <v>39.5</v>
       </c>
       <c r="Q109" t="n">
-        <v>35.4</v>
+        <v>20.8</v>
       </c>
       <c r="R109" t="n">
-        <v>27.6</v>
+        <v>30.9</v>
       </c>
       <c r="S109" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T109" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U109" t="n">
-        <v>39.2</v>
+        <v>32.9</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
@@ -30405,12 +30405,12 @@
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
@@ -30420,12 +30420,12 @@
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 1 HR</t>
+          <t>Last 7 games: 5/23, 1 HR</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 7.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
@@ -30435,104 +30435,104 @@
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>41.05</t>
+          <t>40.91</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>89.93</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>99.8728</t>
+          <t>100.712</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>0.4343</t>
+          <t>0.406</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>0.1693</t>
+          <t>0.1736</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.3145</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>26.54</t>
+          <t>25.75</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>42.33</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>28.78</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>15.7</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>0.1876</t>
+          <t>0.2012</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>88.66</t>
+          <t>85.57</t>
         </is>
       </c>
       <c r="BD109" t="inlineStr">
         <is>
-          <t>0.3506</t>
+          <t>0.3375</t>
         </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
-          <t>0.1393</t>
+          <t>0.1282</t>
         </is>
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>30.02</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="BG109" t="inlineStr"/>
       <c r="BH109" t="inlineStr"/>
       <c r="BI109" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ109" t="inlineStr"/>
@@ -30543,27 +30543,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-16T17:35:00Z</t>
+          <t>2026-08-16T20:10:00Z</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -30573,17 +30573,17 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Logan Henderson</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>701656</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -30592,7 +30592,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>43.9</v>
+        <v>44</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
@@ -30606,26 +30606,26 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>54.1</v>
+        <v>36.4</v>
       </c>
       <c r="Q110" t="n">
-        <v>35.6</v>
+        <v>35.4</v>
       </c>
       <c r="R110" t="n">
-        <v>30.9</v>
+        <v>27.6</v>
       </c>
       <c r="S110" t="n">
-        <v>47.9</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T110" t="n">
         <v>50</v>
       </c>
       <c r="U110" t="n">
-        <v>32.9</v>
+        <v>39.2</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -30639,7 +30639,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
@@ -30681,12 +30681,12 @@
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -30696,119 +30696,119 @@
       </c>
       <c r="AK110" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 1 HR</t>
+          <t>Last 7 games: 7/27, 1 HR</t>
         </is>
       </c>
       <c r="AL110" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 7.2 HR allowed</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>13.31</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>41.05</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>102.9696</t>
+          <t>99.8728</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>0.4343</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>0.1998</t>
+          <t>0.1693</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>0.3111</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>75.83</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>59.22</t>
+          <t>26.54</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>31.01</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>15.3</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>0.1547</t>
+          <t>0.1876</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>8.81</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>35.43</t>
+          <t>35.25</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>88.66</t>
         </is>
       </c>
       <c r="BD110" t="inlineStr">
         <is>
-          <t>0.3937</t>
+          <t>0.3506</t>
         </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
-          <t>0.1546</t>
+          <t>0.1393</t>
         </is>
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="BG110" t="inlineStr"/>
       <c r="BH110" t="inlineStr"/>
       <c r="BI110" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ110" t="inlineStr"/>
@@ -30819,27 +30819,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>572233</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-16T23:20:00Z</t>
+          <t>2026-08-16T17:35:00Z</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -30849,17 +30849,17 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -30868,7 +30868,7 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>43.8</v>
+        <v>43.9</v>
       </c>
       <c r="M111" t="inlineStr">
         <is>
@@ -30886,22 +30886,22 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>42.8</v>
+        <v>54.1</v>
       </c>
       <c r="Q111" t="n">
-        <v>41.2</v>
+        <v>35.6</v>
       </c>
       <c r="R111" t="n">
-        <v>27.6</v>
+        <v>30.9</v>
       </c>
       <c r="S111" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T111" t="n">
         <v>50</v>
       </c>
       <c r="U111" t="n">
-        <v>21.8</v>
+        <v>32.9</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
@@ -30957,12 +30957,12 @@
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
@@ -30972,12 +30972,12 @@
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 1 HR</t>
+          <t>Last 7 games: 5/23, 1 HR</t>
         </is>
       </c>
       <c r="AL111" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM111" t="inlineStr">
@@ -30987,104 +30987,104 @@
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>13.31</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>46.63</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>89.85</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
         <is>
-          <t>101.562</t>
+          <t>102.9696</t>
         </is>
       </c>
       <c r="AR111" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>0.423</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>0.1771</t>
+          <t>0.1998</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr">
         <is>
-          <t>0.3112</t>
+          <t>0.3111</t>
         </is>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>74.31</t>
+          <t>75.83</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>43.62</t>
+          <t>59.22</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>31.01</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>15.3</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>0.2068</t>
+          <t>0.1547</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>35.43</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>89.52</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD111" t="inlineStr">
         <is>
-          <t>0.3814</t>
+          <t>0.3937</t>
         </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
-          <t>0.1492</t>
+          <t>0.1546</t>
         </is>
       </c>
       <c r="BF111" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BG111" t="inlineStr"/>
       <c r="BH111" t="inlineStr"/>
       <c r="BI111" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ111" t="inlineStr"/>
@@ -31095,27 +31095,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>702616</t>
+          <t>572233</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-16T16:15:00Z</t>
+          <t>2026-08-16T23:20:00Z</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -31125,17 +31125,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -31144,7 +31144,7 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
@@ -31158,26 +31158,26 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>27.1</v>
+        <v>42.8</v>
       </c>
       <c r="Q112" t="n">
-        <v>35</v>
+        <v>41.2</v>
       </c>
       <c r="R112" t="n">
         <v>27.6</v>
       </c>
       <c r="S112" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T112" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U112" t="n">
-        <v>41.7</v>
+        <v>21.8</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
@@ -31233,12 +31233,12 @@
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -31248,12 +31248,12 @@
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 1 HR</t>
+          <t>Last 7 games: 3/21, 1 HR</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 20.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
@@ -31263,104 +31263,104 @@
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>89.85</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>98.2468</t>
+          <t>101.562</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>0.3802</t>
+          <t>0.407</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>0.1406</t>
+          <t>0.1771</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>0.3161</t>
+          <t>0.3112</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>74.31</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>43.62</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>28.35</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.2068</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>87.93</t>
+          <t>89.52</t>
         </is>
       </c>
       <c r="BD112" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3814</t>
         </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
-          <t>0.1438</t>
+          <t>0.1492</t>
         </is>
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>27.29</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG112" t="inlineStr"/>
       <c r="BH112" t="inlineStr"/>
       <c r="BI112" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ112" t="inlineStr"/>
@@ -31371,27 +31371,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>702616</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-16T17:40:00Z</t>
+          <t>2026-08-16T16:15:00Z</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -31406,12 +31406,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Casey Mize</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -31438,10 +31438,10 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>30.4</v>
+        <v>27.1</v>
       </c>
       <c r="Q113" t="n">
-        <v>38.7</v>
+        <v>35</v>
       </c>
       <c r="R113" t="n">
         <v>27.6</v>
@@ -31450,10 +31450,10 @@
         <v>92.09999999999999</v>
       </c>
       <c r="T113" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U113" t="n">
-        <v>12</v>
+        <v>41.7</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -31509,134 +31509,134 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Last 7 games: 8/29, 1 HR</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 20.3 HR allowed</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>40.36</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>99.6946</t>
+          <t>98.2468</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
         <is>
-          <t>0.4327</t>
+          <t>0.3802</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>0.1508</t>
+          <t>0.1406</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>0.3161</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>70.27</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>50.97</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>24.33</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>0.1682</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>39.42</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>89.23</t>
+          <t>87.93</t>
         </is>
       </c>
       <c r="BD113" t="inlineStr">
         <is>
-          <t>0.3791</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
-          <t>0.1469</t>
+          <t>0.1438</t>
         </is>
       </c>
       <c r="BF113" t="inlineStr">
         <is>
-          <t>30.53</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="BG113" t="inlineStr"/>
       <c r="BH113" t="inlineStr"/>
       <c r="BI113" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ113" t="inlineStr"/>
@@ -31647,27 +31647,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>694671</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-16T20:05:00Z</t>
+          <t>2026-08-16T17:40:00Z</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -31677,22 +31677,22 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Casey Mize</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>663554</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L114" t="n">
@@ -31714,22 +31714,22 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>39.5</v>
+        <v>30.4</v>
       </c>
       <c r="Q114" t="n">
-        <v>20.8</v>
+        <v>38.7</v>
       </c>
       <c r="R114" t="n">
-        <v>30.9</v>
+        <v>27.6</v>
       </c>
       <c r="S114" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T114" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U114" t="n">
-        <v>27.6</v>
+        <v>12</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -31790,22 +31790,22 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Last 7 games: 4/20, 0 HR</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.3% barrel, 14.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.2% barrel, 11.2 HR allowed</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
@@ -31815,104 +31815,104 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>40.36</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>89.93</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>100.712</t>
+          <t>99.6946</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>0.4327</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>0.1736</t>
+          <t>0.1508</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>0.3145</t>
+          <t>0.349</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>70.27</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>25.75</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>42.33</t>
+          <t>50.97</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>28.78</t>
+          <t>29.76</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>0.2012</t>
+          <t>0.1682</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>39.42</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>85.57</t>
+          <t>89.23</t>
         </is>
       </c>
       <c r="BD114" t="inlineStr">
         <is>
-          <t>0.3375</t>
+          <t>0.3791</t>
         </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
-          <t>0.1282</t>
+          <t>0.1469</t>
         </is>
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BG114" t="inlineStr"/>
       <c r="BH114" t="inlineStr"/>
       <c r="BI114" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ114" t="inlineStr"/>
@@ -39424,7 +39424,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>50</v>
       </c>
       <c r="U142" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
@@ -39518,7 +39518,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
@@ -39528,7 +39528,7 @@
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
@@ -39700,7 +39700,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>50</v>
       </c>
       <c r="U143" t="n">
-        <v>52.5</v>
+        <v>50.3</v>
       </c>
       <c r="V143" t="inlineStr">
         <is>
@@ -39794,7 +39794,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
@@ -39804,7 +39804,7 @@
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Contact streak: 8/23 over last 7 games</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL143" t="inlineStr">
@@ -46528,7 +46528,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="M168" t="inlineStr">
         <is>
@@ -46561,7 +46561,7 @@
         <v>50</v>
       </c>
       <c r="U168" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V168" t="inlineStr">
         <is>
@@ -46622,7 +46622,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ168" t="inlineStr">
@@ -46632,7 +46632,7 @@
       </c>
       <c r="AK168" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Last 7 games: 4/25, 0 HR</t>
         </is>
       </c>
       <c r="AL168" t="inlineStr">
@@ -48135,27 +48135,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>694384</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Nolan Schanuel</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-16T19:15:00Z</t>
+          <t>2026-08-16T20:07:00Z</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -48165,26 +48165,26 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Edward Cabrera</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>665795</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L174" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="M174" t="inlineStr">
         <is>
@@ -48198,26 +48198,26 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P174" t="n">
-        <v>15.2</v>
+        <v>13.9</v>
       </c>
       <c r="Q174" t="n">
-        <v>54.1</v>
+        <v>40.6</v>
       </c>
       <c r="R174" t="n">
-        <v>29.8</v>
+        <v>28.2</v>
       </c>
       <c r="S174" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T174" t="n">
         <v>50</v>
       </c>
       <c r="U174" t="n">
-        <v>16.6</v>
+        <v>39.1</v>
       </c>
       <c r="V174" t="inlineStr">
         <is>
@@ -48231,7 +48231,7 @@
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
@@ -48273,12 +48273,12 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ174" t="inlineStr">
@@ -48288,12 +48288,12 @@
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Contact streak: 8/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.8% barrel, 14.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
@@ -48303,104 +48303,104 @@
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>31.94</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>98.6868</t>
+          <t>97.0926</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>0.3358</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>0.0874</t>
+          <t>0.1113</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>0.2965</t>
+          <t>0.3312</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>67.96</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>21.11</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>0.0897</t>
+          <t>0.1173</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="BD174" t="inlineStr">
         <is>
-          <t>0.4241</t>
+          <t>0.4198</t>
         </is>
       </c>
       <c r="BE174" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.166</t>
         </is>
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>23.86</t>
+          <t>25.33</t>
         </is>
       </c>
       <c r="BG174" t="inlineStr"/>
       <c r="BH174" t="inlineStr"/>
       <c r="BI174" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ174" t="inlineStr"/>
@@ -48411,27 +48411,27 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>694384</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Nolan Schanuel</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-08-16T20:07:00Z</t>
+          <t>2026-08-16T19:15:00Z</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -48441,26 +48441,26 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Edward Cabrera</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>665795</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -48474,26 +48474,26 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P175" t="n">
-        <v>13.9</v>
+        <v>15.2</v>
       </c>
       <c r="Q175" t="n">
-        <v>40.6</v>
+        <v>54.1</v>
       </c>
       <c r="R175" t="n">
-        <v>28.2</v>
+        <v>29.8</v>
       </c>
       <c r="S175" t="n">
-        <v>92.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="T175" t="n">
         <v>50</v>
       </c>
       <c r="U175" t="n">
-        <v>34.5</v>
+        <v>16.6</v>
       </c>
       <c r="V175" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
@@ -48549,12 +48549,12 @@
       </c>
       <c r="AH175" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
@@ -48564,12 +48564,12 @@
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Contact streak: 7/20 over last 7 games</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.8% barrel, 14.9 HR allowed</t>
         </is>
       </c>
       <c r="AM175" t="inlineStr">
@@ -48579,104 +48579,104 @@
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>31.94</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
-          <t>97.0926</t>
+          <t>98.6868</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3358</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>0.1113</t>
+          <t>0.0874</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>0.3312</t>
+          <t>0.2965</t>
         </is>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>67.96</t>
+          <t>71.17</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>21.11</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>0.1173</t>
+          <t>0.0897</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>10.84</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>43.81</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="BD175" t="inlineStr">
         <is>
-          <t>0.4198</t>
+          <t>0.4241</t>
         </is>
       </c>
       <c r="BE175" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>23.86</t>
         </is>
       </c>
       <c r="BG175" t="inlineStr"/>
       <c r="BH175" t="inlineStr"/>
       <c r="BI175" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ175" t="inlineStr"/>
@@ -57016,7 +57016,7 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="M206" t="inlineStr">
         <is>
@@ -57049,7 +57049,7 @@
         <v>78</v>
       </c>
       <c r="U206" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="V206" t="inlineStr">
         <is>
@@ -57110,7 +57110,7 @@
       </c>
       <c r="AI206" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ206" t="inlineStr">
@@ -57120,7 +57120,7 @@
       </c>
       <c r="AK206" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/27, 0 HR</t>
+          <t>Last 7 games: 4/28, 0 HR</t>
         </is>
       </c>
       <c r="AL206" t="inlineStr">
@@ -63867,27 +63867,27 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>694497</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Evan Carter</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>2026-08-16T17:35:00Z</t>
+          <t>2026-08-16T20:05:00Z</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -63902,21 +63902,21 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Michael Soroka</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>647336</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L231" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
@@ -63934,10 +63934,10 @@
         </is>
       </c>
       <c r="P231" t="n">
-        <v>11</v>
+        <v>21.2</v>
       </c>
       <c r="Q231" t="n">
-        <v>35.6</v>
+        <v>20.8</v>
       </c>
       <c r="R231" t="n">
         <v>30.9</v>
@@ -63949,7 +63949,7 @@
         <v>50</v>
       </c>
       <c r="U231" t="n">
-        <v>5.1</v>
+        <v>10.6</v>
       </c>
       <c r="V231" t="inlineStr">
         <is>
@@ -64010,7 +64010,7 @@
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
@@ -64020,119 +64020,119 @@
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>35.72</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>86.18</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>96.3629</t>
+          <t>98.6424</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>0.3674</t>
+          <t>0.3362</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>0.1043</t>
+          <t>0.1218</t>
         </is>
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>0.2997</t>
+          <t>0.2954</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>71.02</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>39.05</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>25.02</t>
+          <t>27.98</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>0.1259</t>
+          <t>0.1317</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>35.43</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>85.57</t>
         </is>
       </c>
       <c r="BD231" t="inlineStr">
         <is>
-          <t>0.3937</t>
+          <t>0.3375</t>
         </is>
       </c>
       <c r="BE231" t="inlineStr">
         <is>
-          <t>0.1546</t>
+          <t>0.1282</t>
         </is>
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="BG231" t="inlineStr"/>
       <c r="BH231" t="inlineStr"/>
       <c r="BI231" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ231" t="inlineStr"/>
@@ -64143,27 +64143,27 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>642851</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Austin Wynns</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-08-16T20:05:00Z</t>
+          <t>2026-08-16T17:35:00Z</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -64173,22 +64173,22 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Michael Soroka</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>647336</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L232" t="n">
@@ -64206,26 +64206,26 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P232" t="n">
-        <v>18.2</v>
+        <v>11</v>
       </c>
       <c r="Q232" t="n">
-        <v>20.8</v>
+        <v>35.6</v>
       </c>
       <c r="R232" t="n">
         <v>30.9</v>
       </c>
       <c r="S232" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T232" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U232" t="n">
-        <v>45</v>
+        <v>5.1</v>
       </c>
       <c r="V232" t="inlineStr">
         <is>
@@ -64239,7 +64239,7 @@
       </c>
       <c r="X232" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y232" t="inlineStr">
@@ -64281,12 +64281,12 @@
       </c>
       <c r="AH232" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI232" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ232" t="inlineStr">
@@ -64296,119 +64296,119 @@
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>Contact streak: 6/14 over last 7 games</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL232" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.3% barrel, 14.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 7.8 HR allowed</t>
         </is>
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN232" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>33.65</t>
+          <t>29.03</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>86.36</t>
+          <t>86.18</t>
         </is>
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>97.9394</t>
+          <t>96.3629</t>
         </is>
       </c>
       <c r="AR232" t="inlineStr">
         <is>
-          <t>0.3276</t>
+          <t>0.3674</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>0.1219</t>
+          <t>0.1043</t>
         </is>
       </c>
       <c r="AT232" t="inlineStr">
         <is>
-          <t>0.2502</t>
+          <t>0.2997</t>
         </is>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>70.69</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>3.68</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>32.45</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>27.86</t>
+          <t>25.02</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>0.1025</t>
+          <t>0.1259</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>35.43</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>85.57</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="BD232" t="inlineStr">
         <is>
-          <t>0.3375</t>
+          <t>0.3937</t>
         </is>
       </c>
       <c r="BE232" t="inlineStr">
         <is>
-          <t>0.1282</t>
+          <t>0.1546</t>
         </is>
       </c>
       <c r="BF232" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="BG232" t="inlineStr"/>
       <c r="BH232" t="inlineStr"/>
       <c r="BI232" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ232" t="inlineStr"/>
@@ -65247,27 +65247,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>642851</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Austin Wynns</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-08-16T16:15:00Z</t>
+          <t>2026-08-16T20:05:00Z</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -65277,17 +65277,17 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Trevor Rogers</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>669432</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
@@ -65296,7 +65296,7 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="M236" t="inlineStr">
         <is>
@@ -65310,26 +65310,26 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P236" t="n">
-        <v>0.3</v>
+        <v>18.2</v>
       </c>
       <c r="Q236" t="n">
-        <v>37.4</v>
+        <v>20.8</v>
       </c>
       <c r="R236" t="n">
-        <v>27.6</v>
+        <v>30.9</v>
       </c>
       <c r="S236" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T236" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U236" t="n">
-        <v>44.9</v>
+        <v>42</v>
       </c>
       <c r="V236" t="inlineStr">
         <is>
@@ -65343,7 +65343,7 @@
       </c>
       <c r="X236" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y236" t="inlineStr">
@@ -65385,12 +65385,12 @@
       </c>
       <c r="AH236" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI236" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ236" t="inlineStr">
@@ -65400,119 +65400,119 @@
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>Contact streak: 13/31 over last 7 games</t>
+          <t>Contact streak: 6/15 over last 7 games</t>
         </is>
       </c>
       <c r="AL236" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM236" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN236" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>33.65</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>86.36</t>
         </is>
       </c>
       <c r="AQ236" t="inlineStr">
         <is>
-          <t>92.9205</t>
+          <t>97.9394</t>
         </is>
       </c>
       <c r="AR236" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3276</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr">
         <is>
-          <t>0.0389</t>
+          <t>0.1219</t>
         </is>
       </c>
       <c r="AT236" t="inlineStr">
         <is>
-          <t>0.2753</t>
+          <t>0.2502</t>
         </is>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>64.66</t>
+          <t>70.69</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>27.71</t>
+          <t>37.71</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>27.86</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>0.0549</t>
+          <t>0.1025</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>89.21</t>
+          <t>85.57</t>
         </is>
       </c>
       <c r="BD236" t="inlineStr">
         <is>
-          <t>0.3879</t>
+          <t>0.3375</t>
         </is>
       </c>
       <c r="BE236" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1282</t>
         </is>
       </c>
       <c r="BF236" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="BG236" t="inlineStr"/>
       <c r="BH236" t="inlineStr"/>
       <c r="BI236" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ236" t="inlineStr"/>
@@ -65523,27 +65523,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>694497</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Evan Carter</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-08-16T20:05:00Z</t>
+          <t>2026-08-16T16:15:00Z</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -65553,17 +65553,17 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Trevor Rogers</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>669432</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
@@ -65590,22 +65590,22 @@
         </is>
       </c>
       <c r="P237" t="n">
-        <v>21.2</v>
+        <v>0.3</v>
       </c>
       <c r="Q237" t="n">
-        <v>20.8</v>
+        <v>37.4</v>
       </c>
       <c r="R237" t="n">
-        <v>30.9</v>
+        <v>27.6</v>
       </c>
       <c r="S237" t="n">
-        <v>71.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T237" t="n">
         <v>50</v>
       </c>
       <c r="U237" t="n">
-        <v>4.5</v>
+        <v>44.9</v>
       </c>
       <c r="V237" t="inlineStr">
         <is>
@@ -65619,7 +65619,7 @@
       </c>
       <c r="X237" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y237" t="inlineStr">
@@ -65661,12 +65661,12 @@
       </c>
       <c r="AH237" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ237" t="inlineStr">
@@ -65676,119 +65676,119 @@
       </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Contact streak: 13/31 over last 7 games</t>
         </is>
       </c>
       <c r="AL237" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.3% barrel, 14.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.3% barrel, 10.2 HR allowed</t>
         </is>
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>5.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>98.6424</t>
+          <t>92.9205</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
-          <t>0.3362</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>0.1218</t>
+          <t>0.0389</t>
         </is>
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>0.2954</t>
+          <t>0.2753</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>71.02</t>
+          <t>64.66</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>39.05</t>
+          <t>27.71</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>0.1317</t>
+          <t>0.0549</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>41.82</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>85.57</t>
+          <t>89.21</t>
         </is>
       </c>
       <c r="BD237" t="inlineStr">
         <is>
-          <t>0.3375</t>
+          <t>0.3879</t>
         </is>
       </c>
       <c r="BE237" t="inlineStr">
         <is>
-          <t>0.1282</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>24.53</t>
         </is>
       </c>
       <c r="BG237" t="inlineStr"/>
       <c r="BH237" t="inlineStr"/>
       <c r="BI237" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ237" t="inlineStr"/>
@@ -71799,22 +71799,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>670032</t>
+          <t>683766</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Nicky Lopez</t>
+          <t>Christian Koss</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -71834,21 +71834,21 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Jacob Lopez</t>
+          <t>Gabriel Hughes</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>682052</t>
+          <t>687312</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L260" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
@@ -71866,13 +71866,13 @@
         </is>
       </c>
       <c r="P260" t="n">
-        <v>2</v>
+        <v>12.1</v>
       </c>
       <c r="Q260" t="n">
-        <v>20.8</v>
+        <v>12.1</v>
       </c>
       <c r="R260" t="n">
-        <v>30.9</v>
+        <v>19.3</v>
       </c>
       <c r="S260" t="n">
         <v>40.2</v>
@@ -71881,7 +71881,7 @@
         <v>50</v>
       </c>
       <c r="U260" t="n">
-        <v>14.1</v>
+        <v>22.4</v>
       </c>
       <c r="V260" t="inlineStr">
         <is>
@@ -71920,7 +71920,7 @@
       </c>
       <c r="AC260" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD260" t="inlineStr"/>
@@ -71937,12 +71937,12 @@
       </c>
       <c r="AH260" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI260" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ260" t="inlineStr">
@@ -71952,119 +71952,119 @@
       </c>
       <c r="AK260" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/14, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL260" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.3% barrel, 14.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.1% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM260" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN260" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>29.75</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>84.52</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="AQ260" t="inlineStr">
         <is>
-          <t>95.1609</t>
+          <t>97.1617</t>
         </is>
       </c>
       <c r="AR260" t="inlineStr">
         <is>
-          <t>0.2571</t>
+          <t>0.3278</t>
         </is>
       </c>
       <c r="AS260" t="inlineStr">
         <is>
-          <t>0.0391</t>
+          <t>0.0942</t>
         </is>
       </c>
       <c r="AT260" t="inlineStr">
         <is>
-          <t>0.2498</t>
+          <t>0.2634</t>
         </is>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>66.58</t>
+          <t>69.65</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>33.59</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>23.25</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>0.0294</t>
+          <t>0.0599</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>85.57</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="BD260" t="inlineStr">
         <is>
-          <t>0.3375</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="BE260" t="inlineStr">
         <is>
-          <t>0.1282</t>
+          <t>0.092</t>
         </is>
       </c>
       <c r="BF260" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>25.5</t>
         </is>
       </c>
       <c r="BG260" t="inlineStr"/>
       <c r="BH260" t="inlineStr"/>
       <c r="BI260" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ260" t="inlineStr"/>
@@ -72075,22 +72075,22 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>683766</t>
+          <t>670032</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Christian Koss</t>
+          <t>Nicky Lopez</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -72110,21 +72110,21 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Gabriel Hughes</t>
+          <t>Jacob Lopez</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>687312</t>
+          <t>682052</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L261" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M261" t="inlineStr">
         <is>
@@ -72142,13 +72142,13 @@
         </is>
       </c>
       <c r="P261" t="n">
-        <v>12.1</v>
+        <v>2</v>
       </c>
       <c r="Q261" t="n">
-        <v>12.1</v>
+        <v>20.8</v>
       </c>
       <c r="R261" t="n">
-        <v>19.3</v>
+        <v>30.9</v>
       </c>
       <c r="S261" t="n">
         <v>40.2</v>
@@ -72157,7 +72157,7 @@
         <v>50</v>
       </c>
       <c r="U261" t="n">
-        <v>22.4</v>
+        <v>10.1</v>
       </c>
       <c r="V261" t="inlineStr">
         <is>
@@ -72196,7 +72196,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr"/>
@@ -72213,12 +72213,12 @@
       </c>
       <c r="AH261" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI261" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ261" t="inlineStr">
@@ -72228,119 +72228,119 @@
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL261" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.1% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.3% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN261" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>84.52</t>
         </is>
       </c>
       <c r="AQ261" t="inlineStr">
         <is>
-          <t>97.1617</t>
+          <t>95.1609</t>
         </is>
       </c>
       <c r="AR261" t="inlineStr">
         <is>
-          <t>0.3278</t>
+          <t>0.2571</t>
         </is>
       </c>
       <c r="AS261" t="inlineStr">
         <is>
-          <t>0.0942</t>
+          <t>0.0391</t>
         </is>
       </c>
       <c r="AT261" t="inlineStr">
         <is>
-          <t>0.2634</t>
+          <t>0.2498</t>
         </is>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>69.65</t>
+          <t>66.58</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>33.59</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>0.0599</t>
+          <t>0.0294</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.57</t>
         </is>
       </c>
       <c r="BD261" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.3375</t>
         </is>
       </c>
       <c r="BE261" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>0.1282</t>
         </is>
       </c>
       <c r="BF261" t="inlineStr">
         <is>
-          <t>25.5</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="BG261" t="inlineStr"/>
       <c r="BH261" t="inlineStr"/>
       <c r="BI261" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ261" t="inlineStr"/>
@@ -76314,7 +76314,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>57.7</v>
+        <v>57.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -76347,7 +76347,7 @@
         <v>78</v>
       </c>
       <c r="U14" t="n">
-        <v>50.3</v>
+        <v>48.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -76408,7 +76408,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -76418,7 +76418,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Contact streak: 9/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-16.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-16.xlsx
@@ -2506,34 +2506,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12854,34 +12850,30 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB45" t="inlineStr"/>
       <c r="AC45" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13978,34 +13970,30 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -18162,34 +18150,30 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -32122,34 +32106,30 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -32406,34 +32386,30 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y115" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -33522,34 +33498,30 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39640,28 +39612,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W141" t="inlineStr"/>
-      <c r="X141" t="inlineStr"/>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y141" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB141" t="inlineStr"/>
       <c r="AC141" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -39916,28 +39892,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W142" t="inlineStr"/>
-      <c r="X142" t="inlineStr"/>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y142" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB142" t="inlineStr"/>
       <c r="AC142" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -77932,34 +77912,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
